--- a/data/trans_dic/P38A-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P38A-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han tomado la tensión alguna vez un/a profesional sanitario/a</t>
+          <t>Población a la que le han tomado la tensión alguna vez un/a profesional sanitario/a (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>82,87; 90,82</t>
+          <t>83,07; 90,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>68,34; 79,13</t>
+          <t>68,93; 79,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86,04; 97,29</t>
+          <t>86,53; 97,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83,02; 90,89</t>
+          <t>83,56; 91,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>80,97; 88,75</t>
+          <t>80,17; 88,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,82; 99,2</t>
+          <t>95,77; 99,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,57; 90,17</t>
+          <t>84,38; 89,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>76,13; 82,95</t>
+          <t>75,94; 82,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>92,17; 97,83</t>
+          <t>91,93; 97,76</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>82,99; 89,61</t>
+          <t>83,72; 89,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>83,28; 89,56</t>
+          <t>83,32; 89,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81,22; 90,62</t>
+          <t>80,94; 90,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89,74; 94,29</t>
+          <t>89,49; 94,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>90,48; 95,1</t>
+          <t>90,87; 95,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>87,76; 93,4</t>
+          <t>87,15; 93,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,54; 91,49</t>
+          <t>87,35; 91,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>87,9; 91,8</t>
+          <t>87,8; 91,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>85,51; 91,14</t>
+          <t>85,59; 91,07</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>84,6; 91,44</t>
+          <t>84,62; 91,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>86,41; 92,72</t>
+          <t>85,69; 92,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,23; 96,06</t>
+          <t>89,56; 96,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>89,09; 94,85</t>
+          <t>89,12; 94,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>90,22; 95,38</t>
+          <t>89,83; 95,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>95,05; 98,61</t>
+          <t>95,11; 98,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>88,24; 92,47</t>
+          <t>87,99; 92,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>89,25; 93,41</t>
+          <t>89,11; 93,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93,5; 96,89</t>
+          <t>93,21; 96,98</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>75,79; 84,36</t>
+          <t>75,87; 84,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>88,74; 94,73</t>
+          <t>89,1; 94,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80,48; 94,42</t>
+          <t>80,23; 94,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84,92; 91,6</t>
+          <t>85,24; 91,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,87; 95,35</t>
+          <t>90,2; 95,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,52; 95,51</t>
+          <t>47,33; 95,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,88; 86,98</t>
+          <t>81,76; 87,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>90,32; 94,36</t>
+          <t>90,53; 94,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>59,42; 93,48</t>
+          <t>60,09; 93,56</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>81,64; 91,38</t>
+          <t>81,39; 91,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>71,78; 82,98</t>
+          <t>71,87; 83,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76,45; 87,9</t>
+          <t>76,81; 87,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89,27; 96,27</t>
+          <t>89,31; 96,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>84,55; 92,75</t>
+          <t>84,72; 92,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,33; 92,01</t>
+          <t>83,78; 91,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,84; 92,76</t>
+          <t>86,94; 92,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>79,86; 86,79</t>
+          <t>79,82; 86,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>82,42; 89,11</t>
+          <t>82,31; 89,09</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>87,17; 94,39</t>
+          <t>86,97; 94,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>79,92; 89,07</t>
+          <t>80,32; 88,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>90,44; 97,29</t>
+          <t>90,59; 97,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>92,07; 97,22</t>
+          <t>92,07; 97,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>88,17; 94,73</t>
+          <t>88,19; 94,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>93,86; 98,8</t>
+          <t>93,74; 98,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>90,86; 95,3</t>
+          <t>90,5; 95,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>85,29; 91,23</t>
+          <t>85,69; 91,14</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>93,37; 97,42</t>
+          <t>93,78; 97,51</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>87,05; 92,06</t>
+          <t>86,87; 92,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>68,98; 76,14</t>
+          <t>68,69; 76,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78,15; 87,44</t>
+          <t>78,24; 87,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>91,61; 95,21</t>
+          <t>91,25; 95,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>77,04; 83,12</t>
+          <t>76,74; 82,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,21; 96,77</t>
+          <t>90,24; 96,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,13; 93,19</t>
+          <t>89,91; 93,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>73,79; 78,49</t>
+          <t>73,79; 78,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>86,18; 93,8</t>
+          <t>86,12; 92,96</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>75,3; 81,46</t>
+          <t>75,62; 81,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>86,42; 90,75</t>
+          <t>86,08; 90,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21,67; 66,83</t>
+          <t>21,8; 66,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79,12; 84,6</t>
+          <t>79,07; 84,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>92,68; 95,86</t>
+          <t>92,72; 95,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>70,67; 76,85</t>
+          <t>70,56; 76,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>78,14; 82,31</t>
+          <t>78,14; 82,22</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>90,07; 92,9</t>
+          <t>90,16; 92,96</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>37,05; 70,5</t>
+          <t>36,32; 70,56</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>83,91; 86,39</t>
+          <t>84,06; 86,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>82,19; 84,76</t>
+          <t>82,27; 84,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>60,45; 84,15</t>
+          <t>60,3; 84,04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>88,5; 90,61</t>
+          <t>88,7; 90,69</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>88,79; 90,81</t>
+          <t>88,86; 90,9</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>81,85; 90,51</t>
+          <t>82,43; 90,63</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>86,69; 88,34</t>
+          <t>86,75; 88,3</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>85,96; 87,58</t>
+          <t>85,97; 87,58</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>73,87; 86,85</t>
+          <t>72,82; 86,61</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han tomado la tensión alguna vez un/a profesional sanitario/a</t>
+          <t>Población a la que le han tomado la tensión alguna vez un/a profesional sanitario/a (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>238992; 261921</t>
+          <t>239591; 261925</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>198822; 230194</t>
+          <t>200515; 231335</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>267955; 303005</t>
+          <t>269485; 303047</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>238474; 261082</t>
+          <t>240023; 261862</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>232866; 255261</t>
+          <t>230576; 255951</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>277521; 287313</t>
+          <t>277380; 287129</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>486858; 519057</t>
+          <t>485742; 517412</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>440433; 479885</t>
+          <t>439329; 478913</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>554002; 588051</t>
+          <t>552564; 587636</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>416278; 449482</t>
+          <t>419931; 449370</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>413043; 444183</t>
+          <t>413216; 442221</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>421036; 469772</t>
+          <t>419565; 469936</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>469130; 492897</t>
+          <t>467836; 493387</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>473303; 497437</t>
+          <t>475305; 496969</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>451924; 480996</t>
+          <t>448791; 480031</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>896749; 937236</t>
+          <t>894834; 935104</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>895759; 935511</t>
+          <t>894757; 933686</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>883616; 941817</t>
+          <t>884416; 941090</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>272519; 294544</t>
+          <t>272569; 294262</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>275273; 295362</t>
+          <t>272969; 295060</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>282019; 303613</t>
+          <t>283050; 304117</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>303815; 323445</t>
+          <t>303920; 323682</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>302583; 319899</t>
+          <t>301289; 319650</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>331830; 344286</t>
+          <t>332065; 344236</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>585175; 613186</t>
+          <t>583497; 614346</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>583640; 610877</t>
+          <t>582735; 610967</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>621942; 644504</t>
+          <t>620014; 645093</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>282553; 314514</t>
+          <t>282856; 313727</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>326556; 348613</t>
+          <t>327877; 348297</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>251547; 295125</t>
+          <t>250765; 294371</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>329446; 355355</t>
+          <t>330717; 355543</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>348056; 369279</t>
+          <t>349340; 368297</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>235571; 454379</t>
+          <t>225163; 452754</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>622947; 661740</t>
+          <t>622023; 663562</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>682156; 712691</t>
+          <t>683757; 713350</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>468353; 736904</t>
+          <t>473661; 737535</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>172813; 193422</t>
+          <t>172288; 192664</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>151615; 175270</t>
+          <t>151796; 175822</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>136641; 157119</t>
+          <t>137285; 157136</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>193498; 208667</t>
+          <t>193586; 208965</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>184807; 202749</t>
+          <t>185197; 202957</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>175630; 191627</t>
+          <t>174492; 191336</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>372045; 397415</t>
+          <t>372487; 397663</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>343253; 373040</t>
+          <t>343053; 373538</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>318964; 344888</t>
+          <t>318565; 344812</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>238821; 258606</t>
+          <t>238283; 258714</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>209450; 233442</t>
+          <t>210498; 233078</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>243860; 262336</t>
+          <t>244264; 262512</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>256932; 271310</t>
+          <t>256937; 271432</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>239276; 257073</t>
+          <t>239327; 256922</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>241276; 253960</t>
+          <t>240952; 253558</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>502470; 527050</t>
+          <t>500510; 526230</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>454962; 486662</t>
+          <t>457117; 486204</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>491779; 513103</t>
+          <t>493927; 513579</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>573551; 606585</t>
+          <t>572410; 607145</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>449914; 496627</t>
+          <t>448051; 497613</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>487854; 545839</t>
+          <t>488435; 545193</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>631268; 656097</t>
+          <t>628840; 655028</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>529369; 571132</t>
+          <t>527302; 569056</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>766127; 821827</t>
+          <t>766396; 822289</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1214999; 1256250</t>
+          <t>1212011; 1254463</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>988349; 1051215</t>
+          <t>988355; 1052661</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1269955; 1382147</t>
+          <t>1269031; 1369741</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>582753; 630432</t>
+          <t>585174; 631471</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>666081; 699399</t>
+          <t>663426; 699010</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>201277; 620634</t>
+          <t>202486; 621965</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>649443; 694449</t>
+          <t>649043; 695928</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>763881; 790084</t>
+          <t>764181; 789925</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>507224; 551601</t>
+          <t>506441; 551016</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1246073; 1312616</t>
+          <t>1246102; 1311227</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1436512; 1481736</t>
+          <t>1437994; 1482699</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>610024; 1160760</t>
+          <t>598042; 1161785</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2855711; 2940312</t>
+          <t>2860774; 2942933</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2769411; 2856110</t>
+          <t>2772382; 2859762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2091288; 2911284</t>
+          <t>2086175; 2907628</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3136959; 3211722</t>
+          <t>3144175; 3214748</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3138530; 3209704</t>
+          <t>3141000; 3213062</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2997333; 3314381</t>
+          <t>3018496; 3318496</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6023651; 6137725</t>
+          <t>6027244; 6135003</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>5934921; 6046536</t>
+          <t>5935473; 6046855</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5260639; 6184803</t>
+          <t>5186081; 6167817</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P38A-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P38A-Provincia-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>83,07; 90,82</t>
+          <t>83,13; 90,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>68,93; 79,52</t>
+          <t>68,78; 79,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86,53; 97,3</t>
+          <t>91,38; 97,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83,56; 91,16</t>
+          <t>82,91; 91,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>80,17; 88,99</t>
+          <t>80,56; 88,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,77; 99,13</t>
+          <t>95,73; 98,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,38; 89,88</t>
+          <t>84,33; 89,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>75,94; 82,78</t>
+          <t>76,01; 82,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>91,93; 97,76</t>
+          <t>94,41; 98,23</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>89,21%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>83,72; 89,59</t>
+          <t>83,03; 89,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>83,32; 89,16</t>
+          <t>83,33; 89,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80,94; 90,65</t>
+          <t>82,66; 91,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89,49; 94,38</t>
+          <t>89,73; 94,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>90,87; 95,01</t>
+          <t>90,64; 95,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>87,15; 93,22</t>
+          <t>87,96; 93,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,35; 91,29</t>
+          <t>87,63; 91,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>87,8; 91,62</t>
+          <t>87,84; 91,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>85,59; 91,07</t>
+          <t>86,4; 91,49</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>84,62; 91,35</t>
+          <t>84,43; 91,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,69; 92,62</t>
+          <t>85,76; 92,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,56; 96,22</t>
+          <t>89,19; 95,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>89,12; 94,92</t>
+          <t>88,81; 94,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>89,83; 95,31</t>
+          <t>89,97; 95,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>95,11; 98,6</t>
+          <t>94,97; 98,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87,99; 92,64</t>
+          <t>87,98; 92,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>89,11; 93,43</t>
+          <t>89,45; 93,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93,21; 96,98</t>
+          <t>92,92; 96,72</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>90,55%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>75,87; 84,15</t>
+          <t>76,06; 84,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>89,1; 94,64</t>
+          <t>88,79; 94,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80,23; 94,18</t>
+          <t>79,9; 92,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85,24; 91,64</t>
+          <t>85,42; 91,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,2; 95,1</t>
+          <t>90,38; 95,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,33; 95,17</t>
+          <t>89,46; 95,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,76; 87,22</t>
+          <t>81,92; 87,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>90,53; 94,45</t>
+          <t>90,51; 94,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>60,09; 93,56</t>
+          <t>87,15; 93,16</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>83,32%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>81,39; 91,02</t>
+          <t>81,65; 91,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>71,87; 83,24</t>
+          <t>72,13; 83,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76,81; 87,91</t>
+          <t>73,58; 84,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89,31; 96,4</t>
+          <t>89,22; 96,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>84,72; 92,85</t>
+          <t>84,56; 92,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>83,78; 91,87</t>
+          <t>82,05; 90,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,94; 92,82</t>
+          <t>87,03; 93,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>79,82; 86,91</t>
+          <t>79,66; 86,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>82,31; 89,09</t>
+          <t>79,43; 86,67</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,16%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>86,97; 94,43</t>
+          <t>86,97; 94,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>80,32; 88,93</t>
+          <t>80,09; 89,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>90,59; 97,36</t>
+          <t>89,7; 96,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>92,07; 97,27</t>
+          <t>91,75; 97,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>88,19; 94,68</t>
+          <t>88,58; 94,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>93,74; 98,64</t>
+          <t>93,94; 98,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>90,5; 95,15</t>
+          <t>90,88; 95,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>85,69; 91,14</t>
+          <t>85,67; 91,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>93,78; 97,51</t>
+          <t>93,02; 96,98</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>88,08%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>86,87; 92,15</t>
+          <t>87,01; 92,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>68,69; 76,29</t>
+          <t>68,71; 76,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78,24; 87,33</t>
+          <t>81,09; 88,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>91,25; 95,05</t>
+          <t>91,43; 95,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>76,74; 82,82</t>
+          <t>76,83; 82,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,24; 96,82</t>
+          <t>88,94; 93,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,91; 93,06</t>
+          <t>89,94; 93,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>73,79; 78,59</t>
+          <t>73,81; 78,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>86,12; 92,96</t>
+          <t>86,04; 90,09</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>67,95%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>75,62; 81,6</t>
+          <t>75,27; 81,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>86,08; 90,7</t>
+          <t>86,4; 90,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21,8; 66,97</t>
+          <t>59,63; 67,18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79,07; 84,78</t>
+          <t>79,47; 85,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>92,72; 95,84</t>
+          <t>92,32; 95,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>70,56; 76,77</t>
+          <t>68,95; 75,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>78,14; 82,22</t>
+          <t>78,25; 82,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>90,16; 92,96</t>
+          <t>90,2; 92,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>36,32; 70,56</t>
+          <t>65,44; 70,17</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>85,65%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>84,06; 86,47</t>
+          <t>84,02; 86,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>82,27; 84,87</t>
+          <t>82,1; 84,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>60,3; 84,04</t>
+          <t>80,98; 84,32</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>88,7; 90,69</t>
+          <t>88,57; 90,61</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>88,86; 90,9</t>
+          <t>88,75; 90,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>82,43; 90,63</t>
+          <t>87,33; 89,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>86,75; 88,3</t>
+          <t>86,67; 88,3</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>85,97; 87,58</t>
+          <t>85,91; 87,51</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>72,82; 86,61</t>
+          <t>84,7; 86,58</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>291379</t>
+          <t>304939</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>284093</t>
+          <t>309411</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>575471</t>
+          <t>614349</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>239591; 261925</t>
+          <t>239756; 261828</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>200515; 231335</t>
+          <t>200102; 231096</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>269485; 303047</t>
+          <t>291353; 312046</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>240023; 261862</t>
+          <t>238155; 262372</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>230576; 255951</t>
+          <t>231695; 255486</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>277380; 287129</t>
+          <t>302572; 312815</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>485742; 517412</t>
+          <t>485464; 516640</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>439329; 478913</t>
+          <t>439738; 479697</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>552564; 587636</t>
+          <t>599437; 623691</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>448209</t>
+          <t>463218</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>467468</t>
+          <t>497683</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>915677</t>
+          <t>960901</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>419931; 449370</t>
+          <t>416491; 448618</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>413216; 442221</t>
+          <t>413287; 443996</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>419565; 469936</t>
+          <t>438651; 484639</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>467836; 493387</t>
+          <t>469082; 492969</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>475305; 496969</t>
+          <t>474121; 498171</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>448791; 480031</t>
+          <t>480676; 511310</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>894834; 935104</t>
+          <t>897668; 936595</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>894757; 933686</t>
+          <t>895163; 934342</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>884416; 941090</t>
+          <t>930612; 985425</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>295106</t>
+          <t>294169</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>339668</t>
+          <t>345698</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>634775</t>
+          <t>639867</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>272569; 294262</t>
+          <t>271960; 295389</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>272969; 295060</t>
+          <t>273191; 295269</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>283050; 304117</t>
+          <t>281842; 302878</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>303920; 323682</t>
+          <t>302866; 323919</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>301289; 319650</t>
+          <t>301737; 319691</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>332065; 344236</t>
+          <t>338463; 350651</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>583497; 614346</t>
+          <t>583457; 614304</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>582735; 610967</t>
+          <t>584958; 612377</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>620014; 645093</t>
+          <t>624760; 650329</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>280605</t>
+          <t>326494</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>383711</t>
+          <t>393479</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>664315</t>
+          <t>719974</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>282856; 313727</t>
+          <t>283575; 314425</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>327877; 348297</t>
+          <t>326769; 348899</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>250765; 294371</t>
+          <t>298126; 345110</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>330717; 355543</t>
+          <t>331411; 355132</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>349340; 368297</t>
+          <t>350022; 369507</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>225163; 452754</t>
+          <t>377488; 404310</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>622023; 663562</t>
+          <t>623198; 662595</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>683757; 713350</t>
+          <t>683595; 713348</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>473661; 737535</t>
+          <t>692918; 740701</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>148457</t>
+          <t>163234</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>184456</t>
+          <t>197093</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>332913</t>
+          <t>360327</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>172288; 192664</t>
+          <t>172827; 192975</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>151796; 175822</t>
+          <t>152363; 175734</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>137285; 157136</t>
+          <t>151325; 173057</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>193586; 208965</t>
+          <t>193399; 208097</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>185197; 202957</t>
+          <t>184846; 202059</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>174492; 191336</t>
+          <t>186101; 205676</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>372487; 397663</t>
+          <t>372852; 398564</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>343053; 373538</t>
+          <t>342383; 372635</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>318565; 344812</t>
+          <t>343512; 374819</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>255275</t>
+          <t>252554</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>249495</t>
+          <t>256036</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>504770</t>
+          <t>508589</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>238283; 258714</t>
+          <t>238270; 257880</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>210498; 233078</t>
+          <t>209918; 233544</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>244264; 262512</t>
+          <t>242823; 260444</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>256937; 271432</t>
+          <t>256042; 271165</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>239327; 256922</t>
+          <t>240370; 257254</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>240952; 253558</t>
+          <t>247764; 260741</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>500510; 526230</t>
+          <t>502576; 526459</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>457117; 486204</t>
+          <t>456995; 485511</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>493927; 513579</t>
+          <t>497143; 518319</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>520968</t>
+          <t>609532</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>792160</t>
+          <t>704370</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1313128</t>
+          <t>1313902</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>572410; 607145</t>
+          <t>573283; 606166</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>448051; 497613</t>
+          <t>448133; 496377</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>488435; 545193</t>
+          <t>583578; 635225</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>628840; 655028</t>
+          <t>630083; 656487</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>527302; 569056</t>
+          <t>527908; 568617</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>766396; 822289</t>
+          <t>686646; 719266</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1212011; 1254463</t>
+          <t>1212423; 1254799</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>988355; 1052661</t>
+          <t>988567; 1053248</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1269031; 1369741</t>
+          <t>1283425; 1343934</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>446540</t>
+          <t>506527</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>529915</t>
+          <t>600611</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>976455</t>
+          <t>1107138</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>585174; 631471</t>
+          <t>582499; 629573</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>663426; 699010</t>
+          <t>665874; 699809</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>202486; 621965</t>
+          <t>475902; 536107</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>649043; 695928</t>
+          <t>652333; 698671</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>764181; 789925</t>
+          <t>760923; 788793</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>506441; 551016</t>
+          <t>573205; 626268</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1246102; 1311227</t>
+          <t>1247864; 1313436</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1437994; 1482699</t>
+          <t>1438658; 1482518</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>598042; 1161785</t>
+          <t>1066336; 1143369</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2686540</t>
+          <t>2920668</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3230964</t>
+          <t>3304382</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5917504</t>
+          <t>6225050</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2860774; 2942933</t>
+          <t>2859498; 2945380</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2772382; 2859762</t>
+          <t>2766571; 2861634</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2086175; 2907628</t>
+          <t>2860688; 2978934</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3144175; 3214748</t>
+          <t>3139531; 3211973</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3141000; 3213062</t>
+          <t>3136841; 3209728</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3018496; 3318496</t>
+          <t>3261548; 3344085</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6027244; 6135003</t>
+          <t>6022229; 6135304</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>5935473; 6046855</t>
+          <t>5931871; 6042142</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5186081; 6167817</t>
+          <t>6155819; 6292662</t>
         </is>
       </c>
     </row>
